--- a/artfynd/A 17462-2026 artfynd.xlsx
+++ b/artfynd/A 17462-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -867,6 +867,636 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132577750</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96328</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Öster om Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>568006</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6505799</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Marktäckande</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132577363</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96328</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Öster om Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>567998</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6505784</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132576958</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sydost Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>568095</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6505853</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132576803</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sydost Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>568115</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6505789</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska spår i basen av fem döda granar</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132577875</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96328</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Öster om Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>567982</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6505796</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132578301</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Öster om Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>568039</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6505839</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17462-2026 artfynd.xlsx
+++ b/artfynd/A 17462-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132526598</v>
       </c>
       <c r="B2" t="n">
-        <v>96406</v>
+        <v>96414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132526688</v>
       </c>
       <c r="B3" t="n">
-        <v>96417</v>
+        <v>96425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>132577750</v>
       </c>
       <c r="B4" t="n">
-        <v>96328</v>
+        <v>96336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>132577363</v>
       </c>
       <c r="B5" t="n">
-        <v>96328</v>
+        <v>96336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>132576958</v>
       </c>
       <c r="B6" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>132576803</v>
       </c>
       <c r="B7" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>132577875</v>
       </c>
       <c r="B8" t="n">
-        <v>96328</v>
+        <v>96336</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 17462-2026 artfynd.xlsx
+++ b/artfynd/A 17462-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132526598</v>
       </c>
       <c r="B2" t="n">
-        <v>96414</v>
+        <v>96424</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132526688</v>
       </c>
       <c r="B3" t="n">
-        <v>96425</v>
+        <v>96435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>132577750</v>
       </c>
       <c r="B4" t="n">
-        <v>96336</v>
+        <v>96346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>132577363</v>
       </c>
       <c r="B5" t="n">
-        <v>96336</v>
+        <v>96346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>132576958</v>
       </c>
       <c r="B6" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>132576803</v>
       </c>
       <c r="B7" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>132577875</v>
       </c>
       <c r="B8" t="n">
-        <v>96336</v>
+        <v>96346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 17462-2026 artfynd.xlsx
+++ b/artfynd/A 17462-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132526598</v>
       </c>
       <c r="B2" t="n">
-        <v>96424</v>
+        <v>96425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132526688</v>
       </c>
       <c r="B3" t="n">
-        <v>96435</v>
+        <v>96436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>132577750</v>
       </c>
       <c r="B4" t="n">
-        <v>96346</v>
+        <v>96347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>132577363</v>
       </c>
       <c r="B5" t="n">
-        <v>96346</v>
+        <v>96347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>132576958</v>
       </c>
       <c r="B6" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>132577875</v>
       </c>
       <c r="B8" t="n">
-        <v>96346</v>
+        <v>96347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 17462-2026 artfynd.xlsx
+++ b/artfynd/A 17462-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>132526598</v>
       </c>
       <c r="B2" t="n">
-        <v>96425</v>
+        <v>96426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132526688</v>
       </c>
       <c r="B3" t="n">
-        <v>96436</v>
+        <v>96437</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>132577750</v>
       </c>
       <c r="B4" t="n">
-        <v>96347</v>
+        <v>96348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>132577363</v>
       </c>
       <c r="B5" t="n">
-        <v>96347</v>
+        <v>96348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>132576958</v>
       </c>
       <c r="B6" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>132577875</v>
       </c>
       <c r="B8" t="n">
-        <v>96347</v>
+        <v>96348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,6 +1497,454 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132768025</v>
+      </c>
+      <c r="B10" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>567980</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6505816</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Hasse Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132767816</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>567983</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6505812</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Hasse Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132769657</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>568015</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6505722</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Hasse Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132767063</v>
+      </c>
+      <c r="B13" t="n">
+        <v>96426</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>568088</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6505848</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Hasse Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17462-2026 artfynd.xlsx
+++ b/artfynd/A 17462-2026 artfynd.xlsx
@@ -1081,7 +1081,7 @@
         <v>132576958</v>
       </c>
       <c r="B6" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 17462-2026 artfynd.xlsx
+++ b/artfynd/A 17462-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132526598</v>
       </c>
       <c r="B2" t="n">
-        <v>96426</v>
+        <v>96427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132526688</v>
       </c>
       <c r="B3" t="n">
-        <v>96437</v>
+        <v>96438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>132577750</v>
       </c>
       <c r="B4" t="n">
-        <v>96348</v>
+        <v>96349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>132577363</v>
       </c>
       <c r="B5" t="n">
-        <v>96348</v>
+        <v>96349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>132576958</v>
       </c>
       <c r="B6" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>132576803</v>
       </c>
       <c r="B7" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>132577875</v>
       </c>
       <c r="B8" t="n">
-        <v>96348</v>
+        <v>96349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>132768025</v>
       </c>
       <c r="B10" t="n">
-        <v>96348</v>
+        <v>96349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>132767816</v>
       </c>
       <c r="B11" t="n">
-        <v>96348</v>
+        <v>96349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>132769657</v>
       </c>
       <c r="B12" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>132767063</v>
       </c>
       <c r="B13" t="n">
-        <v>96426</v>
+        <v>96427</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 17462-2026 artfynd.xlsx
+++ b/artfynd/A 17462-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132526598</v>
       </c>
       <c r="B2" t="n">
-        <v>96427</v>
+        <v>96429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132526688</v>
       </c>
       <c r="B3" t="n">
-        <v>96438</v>
+        <v>96440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>132577750</v>
       </c>
       <c r="B4" t="n">
-        <v>96349</v>
+        <v>96351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>132577363</v>
       </c>
       <c r="B5" t="n">
-        <v>96349</v>
+        <v>96351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>132576958</v>
       </c>
       <c r="B6" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>132577875</v>
       </c>
       <c r="B8" t="n">
-        <v>96349</v>
+        <v>96351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>132768025</v>
       </c>
       <c r="B10" t="n">
-        <v>96349</v>
+        <v>96351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>132767816</v>
       </c>
       <c r="B11" t="n">
-        <v>96349</v>
+        <v>96351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>132769657</v>
       </c>
       <c r="B12" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>132767063</v>
       </c>
       <c r="B13" t="n">
-        <v>96427</v>
+        <v>96429</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 17462-2026 artfynd.xlsx
+++ b/artfynd/A 17462-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132526598</v>
       </c>
       <c r="B2" t="n">
-        <v>96429</v>
+        <v>96430</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132526688</v>
       </c>
       <c r="B3" t="n">
-        <v>96440</v>
+        <v>96441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>132577750</v>
       </c>
       <c r="B4" t="n">
-        <v>96351</v>
+        <v>96352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>132577363</v>
       </c>
       <c r="B5" t="n">
-        <v>96351</v>
+        <v>96352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>132576958</v>
       </c>
       <c r="B6" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>132577875</v>
       </c>
       <c r="B8" t="n">
-        <v>96351</v>
+        <v>96352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>132768025</v>
       </c>
       <c r="B10" t="n">
-        <v>96351</v>
+        <v>96352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>132767816</v>
       </c>
       <c r="B11" t="n">
-        <v>96351</v>
+        <v>96352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>132769657</v>
       </c>
       <c r="B12" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>132767063</v>
       </c>
       <c r="B13" t="n">
-        <v>96429</v>
+        <v>96430</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 17462-2026 artfynd.xlsx
+++ b/artfynd/A 17462-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1945,6 +1945,103 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133163018</v>
+      </c>
+      <c r="B14" t="n">
+        <v>96441</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Södra Granstorp, Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>568086</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6505833</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm, Olle Jonsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17462-2026 artfynd.xlsx
+++ b/artfynd/A 17462-2026 artfynd.xlsx
@@ -1950,7 +1950,7 @@
         <v>133163018</v>
       </c>
       <c r="B14" t="n">
-        <v>96441</v>
+        <v>96444</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 17462-2026 artfynd.xlsx
+++ b/artfynd/A 17462-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132526598</v>
       </c>
       <c r="B2" t="n">
-        <v>96430</v>
+        <v>96433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132526688</v>
       </c>
       <c r="B3" t="n">
-        <v>96441</v>
+        <v>96444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>132577750</v>
       </c>
       <c r="B4" t="n">
-        <v>96352</v>
+        <v>96355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>132577363</v>
       </c>
       <c r="B5" t="n">
-        <v>96352</v>
+        <v>96355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>132576958</v>
       </c>
       <c r="B6" t="n">
-        <v>101330</v>
+        <v>101333</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>132576803</v>
       </c>
       <c r="B7" t="n">
-        <v>57951</v>
+        <v>57954</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>132577875</v>
       </c>
       <c r="B8" t="n">
-        <v>96352</v>
+        <v>96355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>132768025</v>
       </c>
       <c r="B10" t="n">
-        <v>96352</v>
+        <v>96355</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>132767816</v>
       </c>
       <c r="B11" t="n">
-        <v>96352</v>
+        <v>96355</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>132769657</v>
       </c>
       <c r="B12" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>132767063</v>
       </c>
       <c r="B13" t="n">
-        <v>96430</v>
+        <v>96433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 17462-2026 artfynd.xlsx
+++ b/artfynd/A 17462-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132526598</v>
       </c>
       <c r="B2" t="n">
-        <v>96433</v>
+        <v>96434</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132526688</v>
       </c>
       <c r="B3" t="n">
-        <v>96444</v>
+        <v>96445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>132577750</v>
       </c>
       <c r="B4" t="n">
-        <v>96355</v>
+        <v>96356</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>132577363</v>
       </c>
       <c r="B5" t="n">
-        <v>96355</v>
+        <v>96356</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>132576958</v>
       </c>
       <c r="B6" t="n">
-        <v>101333</v>
+        <v>101334</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>132577875</v>
       </c>
       <c r="B8" t="n">
-        <v>96355</v>
+        <v>96356</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>132768025</v>
       </c>
       <c r="B10" t="n">
-        <v>96355</v>
+        <v>96356</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>132767816</v>
       </c>
       <c r="B11" t="n">
-        <v>96355</v>
+        <v>96356</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>132769657</v>
       </c>
       <c r="B12" t="n">
-        <v>99125</v>
+        <v>99126</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>132767063</v>
       </c>
       <c r="B13" t="n">
-        <v>96433</v>
+        <v>96434</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>133163018</v>
       </c>
       <c r="B14" t="n">
-        <v>96444</v>
+        <v>96445</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 17462-2026 artfynd.xlsx
+++ b/artfynd/A 17462-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132526598</v>
       </c>
       <c r="B2" t="n">
-        <v>96434</v>
+        <v>96436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132526688</v>
       </c>
       <c r="B3" t="n">
-        <v>96445</v>
+        <v>96447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>132577750</v>
       </c>
       <c r="B4" t="n">
-        <v>96356</v>
+        <v>96358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>132577363</v>
       </c>
       <c r="B5" t="n">
-        <v>96356</v>
+        <v>96358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>132576958</v>
       </c>
       <c r="B6" t="n">
-        <v>101334</v>
+        <v>101338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>132576803</v>
       </c>
       <c r="B7" t="n">
-        <v>57954</v>
+        <v>57955</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>132577875</v>
       </c>
       <c r="B8" t="n">
-        <v>96356</v>
+        <v>96358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>132768025</v>
       </c>
       <c r="B10" t="n">
-        <v>96356</v>
+        <v>96358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>132767816</v>
       </c>
       <c r="B11" t="n">
-        <v>96356</v>
+        <v>96358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>132769657</v>
       </c>
       <c r="B12" t="n">
-        <v>99126</v>
+        <v>99130</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>132767063</v>
       </c>
       <c r="B13" t="n">
-        <v>96434</v>
+        <v>96436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>133163018</v>
       </c>
       <c r="B14" t="n">
-        <v>96445</v>
+        <v>96447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 17462-2026 artfynd.xlsx
+++ b/artfynd/A 17462-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132526598</v>
+        <v>132577022</v>
       </c>
       <c r="B2" t="n">
-        <v>96436</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Södra Granstorp, Södra Granstorp, Ög</t>
+          <t>Sydost Södra Granstorp, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568101</v>
+        <v>568074</v>
       </c>
       <c r="R2" t="n">
-        <v>6505847</v>
+        <v>6505826</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,66 +757,70 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132526688</v>
+        <v>132769799</v>
       </c>
       <c r="B3" t="n">
-        <v>96447</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2667</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Södra Granstorp, Södra Granstorp, Ög</t>
+          <t>Södra Granstorp, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568101</v>
+        <v>568082</v>
       </c>
       <c r="R3" t="n">
-        <v>6505847</v>
+        <v>6505823</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +844,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -851,28 +868,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Lena Lundin Johansson, Hasse Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132577750</v>
+        <v>132526688</v>
       </c>
       <c r="B4" t="n">
-        <v>96358</v>
+        <v>96512</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,41 +898,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>2667</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öster om Södra Granstorp, Ög</t>
+          <t>Södra Granstorp, Södra Granstorp, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568006</v>
+        <v>568101</v>
       </c>
       <c r="R4" t="n">
-        <v>6505799</v>
+        <v>6505847</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -946,40 +960,34 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Marktäckande</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132577363</v>
+        <v>133163018</v>
       </c>
       <c r="B5" t="n">
-        <v>96358</v>
+        <v>96512</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,41 +995,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>2667</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öster om Södra Granstorp, Ög</t>
+          <t>Södra Granstorp, Södra Granstorp, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567998</v>
+        <v>568086</v>
       </c>
       <c r="R5" t="n">
-        <v>6505784</v>
+        <v>6505833</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1045,12 +1049,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1059,29 +1063,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm, Olle Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132576958</v>
+        <v>132526598</v>
       </c>
       <c r="B6" t="n">
-        <v>101338</v>
+        <v>96501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,41 +1092,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sydost Södra Granstorp, Ög</t>
+          <t>Södra Granstorp, Södra Granstorp, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568095</v>
+        <v>568101</v>
       </c>
       <c r="R6" t="n">
-        <v>6505853</v>
+        <v>6505847</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1161,72 +1160,67 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132576803</v>
+        <v>132767063</v>
       </c>
       <c r="B7" t="n">
-        <v>57955</v>
+        <v>96501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2671</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sydost Södra Granstorp, Ög</t>
+          <t>Södra Granstorp, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568115</v>
+        <v>568088</v>
       </c>
       <c r="R7" t="n">
-        <v>6505789</v>
+        <v>6505848</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1253,17 +1247,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska spår i basen av fem döda granar</t>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,28 +1271,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Lena Lundin Johansson, Hasse Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132577875</v>
+        <v>132577363</v>
       </c>
       <c r="B8" t="n">
-        <v>96358</v>
+        <v>96423</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567982</v>
+        <v>567998</v>
       </c>
       <c r="R8" t="n">
-        <v>6505796</v>
+        <v>6505784</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,10 +1392,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132578301</v>
+        <v>132577750</v>
       </c>
       <c r="B9" t="n">
-        <v>5179</v>
+        <v>96423</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1403,32 +1403,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>2810</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1436,10 +1431,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568039</v>
+        <v>568006</v>
       </c>
       <c r="R9" t="n">
-        <v>6505839</v>
+        <v>6505799</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,6 +1467,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Marktäckande</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132768025</v>
+        <v>132577875</v>
       </c>
       <c r="B10" t="n">
-        <v>96358</v>
+        <v>96423</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1534,14 +1534,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Södra Granstorp, Ög</t>
+          <t>Öster om Södra Granstorp, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567980</v>
+        <v>567982</v>
       </c>
       <c r="R10" t="n">
-        <v>6505816</v>
+        <v>6505796</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1568,22 +1568,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1599,12 +1589,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Hasse Andersson</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1614,7 +1604,7 @@
         <v>132767816</v>
       </c>
       <c r="B11" t="n">
-        <v>96358</v>
+        <v>96423</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,32 +1713,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132769657</v>
+        <v>132768025</v>
       </c>
       <c r="B12" t="n">
-        <v>99130</v>
+        <v>96423</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1762,10 +1752,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568015</v>
+        <v>567980</v>
       </c>
       <c r="R12" t="n">
-        <v>6505722</v>
+        <v>6505816</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1787,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1807,7 +1797,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1835,10 +1825,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132767063</v>
+        <v>132784831</v>
       </c>
       <c r="B13" t="n">
-        <v>96436</v>
+        <v>91937</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1846,27 +1836,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2671</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1874,10 +1863,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>568088</v>
+        <v>568033</v>
       </c>
       <c r="R13" t="n">
-        <v>6505848</v>
+        <v>6505799</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1907,19 +1896,9 @@
           <t>2026-04-25</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:25</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1947,10 +1926,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133163018</v>
+        <v>88799898</v>
       </c>
       <c r="B14" t="n">
-        <v>96485</v>
+        <v>92567</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,37 +1937,44 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2667</v>
+        <v>6031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Södra Granstorp, Södra Granstorp, Ög</t>
+          <t>Södra Granstorp O 480 m, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>568086</v>
+        <v>568131</v>
       </c>
       <c r="R14" t="n">
-        <v>6505833</v>
+        <v>6505868</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2012,12 +1998,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2020-10-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2020-10-30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2026,21 +2012,876 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström, Jan-Erik Axelsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132526677</v>
+      </c>
+      <c r="B15" t="n">
+        <v>81031</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6444</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skriftlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Graphis scripta</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Södra Granstorp, Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>568101</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6505847</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>Eva Siljeholm</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Eva Siljeholm, Olle Jonsson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132526050</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Södra Granstorp, Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>567964</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6505789</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132576803</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sydost Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>568115</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6505789</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska spår i basen av fem döda granar</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132578021</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Öster om Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>567964</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6505772</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132578301</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Öster om Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>568039</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6505839</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132769657</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>568015</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6505722</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Hasse Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121746503</v>
+      </c>
+      <c r="B21" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mossen ONO-O 825 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>567877</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6505876</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-12-26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-12-26</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132576958</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sydost Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>568095</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6505853</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17462-2026 artfynd.xlsx
+++ b/artfynd/A 17462-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132577022</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132769799</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132526688</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133163018</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1175,6 +1200,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132526598</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1287,6 +1317,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132767063</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1389,6 +1424,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132577363</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1496,6 +1536,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132577750</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1598,6 +1643,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132577875</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1710,6 +1760,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132767816</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1822,6 +1877,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132768025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1923,6 +1983,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132784831</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2033,6 +2098,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88799898</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2130,6 +2200,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132526677</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2227,6 +2302,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132526050</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2337,6 +2417,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132576803</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2442,6 +2527,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132578021</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2549,6 +2639,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132578301</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2661,6 +2756,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132769657</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2780,6 +2880,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121746503</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2882,8 +2987,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132576958</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>